--- a/data/trans_orig/P36B13-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B13-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>201321</t>
+          <t>197230</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>249927</t>
+          <t>244822</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>258868</t>
+          <t>261411</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>312672</t>
+          <t>311189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>473091</t>
+          <t>471531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>545480</t>
+          <t>543354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,65%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157474</t>
+          <t>157173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>204500</t>
+          <t>204590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133113</t>
+          <t>133902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>178461</t>
+          <t>176099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>302825</t>
+          <t>307828</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>366013</t>
+          <t>370103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>155473</t>
+          <t>154788</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>200087</t>
+          <t>199886</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>141011</t>
+          <t>143999</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>184438</t>
+          <t>185778</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>310246</t>
+          <t>312133</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>371692</t>
+          <t>376663</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65668</t>
+          <t>68017</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97893</t>
+          <t>102618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44896</t>
+          <t>44858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73448</t>
+          <t>72400</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119627</t>
+          <t>118534</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162082</t>
+          <t>164715</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>1665</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6489</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>19075</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>248103</t>
+          <t>248614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305511</t>
+          <t>302708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>308663</t>
+          <t>302499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>370569</t>
+          <t>367042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>568306</t>
+          <t>566638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>653419</t>
+          <t>656222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>275169</t>
+          <t>277807</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>337894</t>
+          <t>338251</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308614</t>
+          <t>309974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>368594</t>
+          <t>371254</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>599901</t>
+          <t>603205</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>686069</t>
+          <t>685752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>279624</t>
+          <t>282518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>339371</t>
+          <t>342688</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>247236</t>
+          <t>248384</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>303750</t>
+          <t>304980</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>547366</t>
+          <t>541546</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>630934</t>
+          <t>626381</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,41%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89887</t>
+          <t>91190</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133165</t>
+          <t>130998</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>67030</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102462</t>
+          <t>102300</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>167199</t>
+          <t>167436</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>222198</t>
+          <t>220590</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>28410</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12185</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>15031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34979</t>
+          <t>34410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157495</t>
+          <t>158262</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>208235</t>
+          <t>206474</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>189666</t>
+          <t>190828</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>240165</t>
+          <t>243464</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>362458</t>
+          <t>362850</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>434607</t>
+          <t>432662</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>190154</t>
+          <t>191176</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>241559</t>
+          <t>244324</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>231252</t>
+          <t>231723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>283794</t>
+          <t>284275</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>433436</t>
+          <t>433288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>507905</t>
+          <t>507400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>233348</t>
+          <t>234656</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>288162</t>
+          <t>289008</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>228953</t>
+          <t>226464</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>281641</t>
+          <t>278740</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>480822</t>
+          <t>479531</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>556105</t>
+          <t>551887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>77007</t>
+          <t>75176</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>113602</t>
+          <t>111929</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>38350</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65680</t>
+          <t>65754</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>120424</t>
+          <t>121932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>167456</t>
+          <t>169369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10545</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19068</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>242459</t>
+          <t>242727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>300046</t>
+          <t>296981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>341314</t>
+          <t>339329</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>404044</t>
+          <t>405633</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>596621</t>
+          <t>602085</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>684358</t>
+          <t>685647</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,99%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>261726</t>
+          <t>265160</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318622</t>
+          <t>320708</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>303559</t>
+          <t>300997</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>362643</t>
+          <t>365571</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>588443</t>
+          <t>586574</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>666649</t>
+          <t>666642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>238925</t>
+          <t>237773</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>292749</t>
+          <t>290989</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>227467</t>
+          <t>228473</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>284277</t>
+          <t>283295</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>479935</t>
+          <t>479757</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>559029</t>
+          <t>559372</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>70971</t>
+          <t>71264</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>106960</t>
+          <t>106329</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>44629</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74189</t>
+          <t>73557</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>121701</t>
+          <t>125224</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>168272</t>
+          <t>170216</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,69%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,82 +3244,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>11683</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6170</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>20689</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>26295</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>17303</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>38760</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,88%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>11683</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>5943</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>20306</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>26295</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>17190</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>37492</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>897334</t>
+          <t>899003</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1001461</t>
+          <t>1004642</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1153062</t>
+          <t>1151031</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1276601</t>
+          <t>1270230</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2077914</t>
+          <t>2083449</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2243588</t>
+          <t>2238168</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>936667</t>
+          <t>935850</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1045827</t>
+          <t>1046921</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1023676</t>
+          <t>1029472</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1138553</t>
+          <t>1138552</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2002530</t>
+          <t>1998594</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2156320</t>
+          <t>2154891</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>961804</t>
+          <t>961148</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1067920</t>
+          <t>1071612</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>897494</t>
+          <t>899730</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1003386</t>
+          <t>1009133</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1888142</t>
+          <t>1885584</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2032748</t>
+          <t>2039403</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>338724</t>
+          <t>338570</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>412252</t>
+          <t>411121</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>222887</t>
+          <t>219845</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>280751</t>
+          <t>279759</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>580748</t>
+          <t>576099</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>672448</t>
+          <t>670743</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>34685</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>61061</t>
+          <t>60979</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17366</t>
+          <t>17628</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>37412</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55902</t>
+          <t>56560</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>89227</t>
+          <t>89736</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -4368,32 +4368,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>174943</t>
+          <t>193689</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155297</t>
+          <t>171001</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>197128</t>
+          <t>216885</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4403,32 +4403,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>249495</t>
+          <t>275079</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>231898</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>270722</t>
+          <t>297823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4438,32 +4438,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>424438</t>
+          <t>468767</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>391663</t>
+          <t>436464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>451664</t>
+          <t>503365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -4481,32 +4481,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>252046</t>
+          <t>272913</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>224193</t>
+          <t>243339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281251</t>
+          <t>299727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4516,32 +4516,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>275317</t>
+          <t>295590</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254488</t>
+          <t>274240</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>295135</t>
+          <t>318879</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4551,32 +4551,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>527363</t>
+          <t>568503</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>493917</t>
+          <t>533758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>563980</t>
+          <t>607127</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -4594,32 +4594,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>177595</t>
+          <t>187134</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>151491</t>
+          <t>163417</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209524</t>
+          <t>219317</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4629,32 +4629,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>125743</t>
+          <t>135091</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109572</t>
+          <t>117991</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144169</t>
+          <t>155082</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4664,32 +4664,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>303337</t>
+          <t>322225</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>272583</t>
+          <t>288716</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>341580</t>
+          <t>356555</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -4707,32 +4707,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23059</t>
+          <t>29006</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14490</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37425</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4742,32 +4742,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>22487</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13636</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>33054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4777,32 +4777,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43598</t>
+          <t>51493</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>37964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59009</t>
+          <t>68642</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -4820,32 +4820,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5489</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14014</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4855,32 +4855,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4890,32 +4890,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4933,17 +4933,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>633131</t>
+          <t>688427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>633131</t>
+          <t>688427</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>633131</t>
+          <t>688427</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4968,17 +4968,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>673131</t>
+          <t>730367</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>673131</t>
+          <t>730367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>673131</t>
+          <t>730367</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5003,17 +5003,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1306262</t>
+          <t>1418794</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1306262</t>
+          <t>1418794</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1306262</t>
+          <t>1418794</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5050,32 +5050,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>198035</t>
+          <t>221006</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94599</t>
+          <t>196582</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>259468</t>
+          <t>251159</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5085,32 +5085,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>279181</t>
+          <t>308659</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>257394</t>
+          <t>285606</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>302686</t>
+          <t>333138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5120,32 +5120,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>477216</t>
+          <t>529666</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>312884</t>
+          <t>492931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>549775</t>
+          <t>563560</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -5163,32 +5163,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>400662</t>
+          <t>434258</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188038</t>
+          <t>402478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>518404</t>
+          <t>468413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5198,32 +5198,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>415670</t>
+          <t>465725</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>390080</t>
+          <t>435361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>440828</t>
+          <t>495342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5233,32 +5233,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>816332</t>
+          <t>899984</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>555132</t>
+          <t>857011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>939117</t>
+          <t>945015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -5276,32 +5276,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>281959</t>
+          <t>317586</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134970</t>
+          <t>283526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>372774</t>
+          <t>354715</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5311,32 +5311,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>232151</t>
+          <t>262764</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208675</t>
+          <t>238437</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257311</t>
+          <t>290764</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5346,32 +5346,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>514110</t>
+          <t>580350</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>347230</t>
+          <t>536112</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>595512</t>
+          <t>625893</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>29,56%</t>
         </is>
       </c>
     </row>
@@ -5389,32 +5389,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58091</t>
+          <t>64102</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>47320</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85913</t>
+          <t>86274</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5424,32 +5424,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23389</t>
+          <t>25239</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15626</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33172</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5459,32 +5459,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>81480</t>
+          <t>89341</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54611</t>
+          <t>69121</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106091</t>
+          <t>114224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -5502,32 +5502,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>253280</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>759191</t>
+          <t>23175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5537,17 +5537,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>259215</t>
+          <t>17780</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>886092</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5615,17 +5615,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1192027</t>
+          <t>1048052</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>956326</t>
+          <t>1069068</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>956326</t>
+          <t>1069068</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>956326</t>
+          <t>1069068</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2148353</t>
+          <t>2117121</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2148353</t>
+          <t>2117121</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2148353</t>
+          <t>2117121</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5732,32 +5732,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>197161</t>
+          <t>224579</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>171782</t>
+          <t>198414</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>225044</t>
+          <t>253795</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5767,32 +5767,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>462703</t>
+          <t>295922</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>271721</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>719720</t>
+          <t>321102</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5802,32 +5802,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>659864</t>
+          <t>520500</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>506538</t>
+          <t>486186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>969945</t>
+          <t>559328</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -5845,32 +5845,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>281693</t>
+          <t>319748</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>251940</t>
+          <t>288275</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>312313</t>
+          <t>350984</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>261442</t>
+          <t>307711</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122043</t>
+          <t>283696</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349097</t>
+          <t>333833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>543135</t>
+          <t>627460</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369833</t>
+          <t>582063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>638574</t>
+          <t>670150</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -5958,32 +5958,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>174318</t>
+          <t>199119</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>145926</t>
+          <t>171361</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>205406</t>
+          <t>235648</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>183758</t>
+          <t>177339</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>79117</t>
+          <t>154102</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>262643</t>
+          <t>202228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>358076</t>
+          <t>376459</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>246280</t>
+          <t>337521</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>446130</t>
+          <t>415989</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -6071,32 +6071,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48324</t>
+          <t>56185</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33254</t>
+          <t>39602</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68772</t>
+          <t>76260</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>26966</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11910</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>40338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>72645</t>
+          <t>83151</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45999</t>
+          <t>64006</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99442</t>
+          <t>108143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -6184,67 +6184,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3638</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>14385</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6297,17 +6297,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6332,17 +6332,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>932707</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>932707</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>932707</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1637388</t>
+          <t>1614649</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1637388</t>
+          <t>1614649</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1637388</t>
+          <t>1614649</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6414,32 +6414,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>264663</t>
+          <t>280775</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>237498</t>
+          <t>253447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>291237</t>
+          <t>308357</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6449,32 +6449,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>363966</t>
+          <t>403510</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>292781</t>
+          <t>376313</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>399621</t>
+          <t>431551</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6484,32 +6484,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>628630</t>
+          <t>684286</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>553653</t>
+          <t>645163</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>669136</t>
+          <t>727002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -6527,32 +6527,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>339569</t>
+          <t>352774</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>308020</t>
+          <t>325664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>370983</t>
+          <t>387811</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6562,32 +6562,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>366001</t>
+          <t>391152</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>299347</t>
+          <t>364573</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>403670</t>
+          <t>419287</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6597,32 +6597,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>705571</t>
+          <t>743927</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>629096</t>
+          <t>704779</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>758737</t>
+          <t>788308</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -6640,32 +6640,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>235765</t>
+          <t>261320</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>205709</t>
+          <t>229192</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>268163</t>
+          <t>293644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6675,32 +6675,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>310787</t>
+          <t>262641</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>247020</t>
+          <t>233641</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>447982</t>
+          <t>289210</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6710,32 +6710,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>546552</t>
+          <t>523961</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>481974</t>
+          <t>484413</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>712409</t>
+          <t>571171</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -6753,32 +6753,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>70396</t>
+          <t>78088</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54918</t>
+          <t>60782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>93126</t>
+          <t>101391</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6788,32 +6788,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>48994</t>
+          <t>56570</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>42680</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64581</t>
+          <t>73208</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6823,32 +6823,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>119390</t>
+          <t>134659</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>92871</t>
+          <t>109987</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>144321</t>
+          <t>162218</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -6866,32 +6866,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15439</t>
+          <t>16169</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8588</t>
+          <t>8816</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26352</t>
+          <t>28676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>675</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6936,17 +6936,17 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>8779</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26759</t>
+          <t>27284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -6979,17 +6979,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989127</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989127</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>925832</t>
+          <t>989127</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7014,17 +7014,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1090369</t>
+          <t>1114549</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1090369</t>
+          <t>1114549</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1090369</t>
+          <t>1114549</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7049,17 +7049,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2016201</t>
+          <t>2103677</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2016201</t>
+          <t>2103677</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2016201</t>
+          <t>2103677</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>834803</t>
+          <t>920049</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>614773</t>
+          <t>863882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>917807</t>
+          <t>980071</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7131,32 +7131,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1355346</t>
+          <t>1283169</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1189617</t>
+          <t>1236670</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1757464</t>
+          <t>1332745</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7166,32 +7166,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2190148</t>
+          <t>2203219</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1961109</t>
+          <t>2124183</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2712969</t>
+          <t>2269486</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -7209,32 +7209,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1273970</t>
+          <t>1379694</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>933861</t>
+          <t>1318938</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1389789</t>
+          <t>1448922</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7244,32 +7244,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1318430</t>
+          <t>1460178</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1073259</t>
+          <t>1406293</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1431180</t>
+          <t>1512560</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7279,32 +7279,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2592400</t>
+          <t>2839873</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2244608</t>
+          <t>2754922</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2778971</t>
+          <t>2918886</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>40,24%</t>
         </is>
       </c>
     </row>
@@ -7322,32 +7322,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>869637</t>
+          <t>965159</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>686162</t>
+          <t>899851</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>956248</t>
+          <t>1028300</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7357,32 +7357,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>852439</t>
+          <t>837836</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>719237</t>
+          <t>794643</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1025998</t>
+          <t>890390</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7392,32 +7392,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1722076</t>
+          <t>1802995</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1511104</t>
+          <t>1729827</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1922434</t>
+          <t>1880143</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -7435,32 +7435,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>199870</t>
+          <t>227382</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>154996</t>
+          <t>193132</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>237981</t>
+          <t>267863</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7470,32 +7470,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>117243</t>
+          <t>131262</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>92219</t>
+          <t>109331</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>141364</t>
+          <t>156911</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7505,32 +7505,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>317113</t>
+          <t>358644</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>266273</t>
+          <t>314570</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>367453</t>
+          <t>405004</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -7548,32 +7548,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>277391</t>
+          <t>36395</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31995</t>
+          <t>25454</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1070221</t>
+          <t>53642</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7583,32 +7583,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>16828</t>
+          <t>24682</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7618,32 +7618,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>286466</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>36958</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1124660</t>
+          <t>68136</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -7661,17 +7661,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3455671</t>
+          <t>3528680</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7696,17 +7696,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3652534</t>
+          <t>3725560</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7731,17 +7731,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7108204</t>
+          <t>7254240</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
